--- a/output/Data and Chart Outputs/henry_hub_daily.xlsx
+++ b/output/Data and Chart Outputs/henry_hub_daily.xlsx
@@ -839,7 +839,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Last run's source: EIA history XLS (RNGWHHDd.xls)</t>
+          <t>Last run's source: EIA API v2 (RNGWHHD)</t>
         </is>
       </c>
     </row>
